--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-14203567.65</v>
+        <v>-11466828.86</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,127 +1309,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-3.38</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.87</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-13742472.04</v>
+        <v>-14203567.65</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-13024441.49</v>
+        <v>-13742472.04</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,42 +2302,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2347,32 +2347,32 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-15219264.41</v>
+        <v>-13024441.49</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,275 +2733,275 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>174412447.1531792</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-15219264.41</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>16.48</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>6621</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>174548805.8444284</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-15318493.73</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.3966079340163287</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>16.2287225844376</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>12.47062478259823</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>6844</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
         <is>
           <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>106.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>467.073</t>
+          <t>232.177</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.61</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>117.35</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>128.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>127.03</t>
+          <t>126.81</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.89</t>
+          <t>-141.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>49320826.0</t>
+          <t>24628089.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>48856151.4</t>
+          <t>39488115.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>73586258.9</t>
+          <t>66316644.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>286214994.92</t>
+          <t>280411936.8</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-24730107</t>
+          <t>-26828529</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-18681840.35212285</t>
+          <t>-18164402.41061377</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-14063047.64</v>
+        <v>-15318493.73</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-29.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>413.715</t>
+          <t>467.073</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>-33.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>118.78</t>
+          <t>117.35</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>127.03</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.92</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-138.36</t>
+          <t>-139.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>44635158.0</t>
+          <t>49320826.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>85278381.6</t>
+          <t>48856151.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>72239823.7</t>
+          <t>73586258.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>286227361.02</t>
+          <t>286214994.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>13038557</t>
+          <t>-24730107</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-19521620.84610226</t>
+          <t>-18681840.35212285</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-14412951.9</v>
+        <v>-14063047.64</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>251.273</t>
+          <t>413.715</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>118.78</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>129.02</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>127.27</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-15.92</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-6.05</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-5.22</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-138.36</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>174412447.1531792</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>44635158.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>85278381.6</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>72239823.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>286227361.02</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>13038557</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-19521620.84610226</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-14412951.9</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-28.33</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>16.48</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>6621</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>110.5</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>111.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>120.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>129.3</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-17.81</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-5.01</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-136.84</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>174548805.8444284</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>27562773.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>89666018.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>73099289.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>289232531.04</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>16566729</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-20450469.74495029</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-13896031</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-26.67</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.3966079340163287</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>16.2287225844376</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>12.47062478259823</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>17.04</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>6844</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>460.487</t>
+          <t>251.273</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>121.88</t>
+          <t>120.38</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>129.49</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>127.69</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-17.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.20</t>
+          <t>-136.84</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>51293733.0</t>
+          <t>27562773.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>92108454.2</t>
+          <t>89666018.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>75715057.4</t>
+          <t>73099289.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>289684789.64</t>
+          <t>289232531.04</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>16393396</t>
+          <t>16566729</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-21642185.88004575</t>
+          <t>-20450469.74495029</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-10832101.64</v>
+        <v>-13896031</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,42 +4625,42 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>110.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>110.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>647.681</t>
+          <t>460.487</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.28</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>123.08</t>
+          <t>121.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>129.67</t>
+          <t>129.49</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>127.96</t>
+          <t>127.69</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.13</t>
+          <t>-22.93</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-133.18</t>
+          <t>-135.20</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71468267.0</t>
+          <t>51293733.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>93145173.8</t>
+          <t>92108454.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>75609500.8</t>
+          <t>75715057.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>290466928.82</t>
+          <t>289684789.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17535673</t>
+          <t>16393396</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-23607655.74114843</t>
+          <t>-21642185.88004575</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-8610801.789999999</v>
+        <v>-10832101.64</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-27.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>112.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>110.5</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>109.5</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>109.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-8.81</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2119.761</t>
+          <t>647.681</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-18.28</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>516</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.74</t>
+          <t>-8.75</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>124.38</t>
+          <t>123.08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>129.96</t>
+          <t>129.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>128.21</t>
+          <t>127.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-33.06</t>
+          <t>-29.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-130.76</t>
+          <t>-133.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>174548805.8444284</t>
+          <t>174412447.1531792</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>231431977.0</t>
+          <t>71468267.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>98316366.4</t>
+          <t>93145173.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>73950494.4</t>
+          <t>75609500.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>290728536.04</t>
+          <t>290466928.82</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>24365872</t>
+          <t>17535673</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-26334356.45986556</t>
+          <t>-23607655.74114843</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-7291544.86</v>
+        <v>-8610801.789999999</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-27.00</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.3966079340163287</t>
+          <t>5.250774319168377</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>16.2287225844376</t>
+          <t>25.47364171666412</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>12.47062478259823</t>
+          <t>14.58538535259029</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-11466828.86</v>
+        <v>-9431051.609999999</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-14203567.65</v>
+        <v>-11466828.86</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,127 +1740,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-6.47</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-5.31</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-13742472.04</v>
+        <v>-14203567.65</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-13024441.49</v>
+        <v>-13742472.04</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,32 +2778,32 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-15219264.41</v>
+        <v>-13024441.49</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,275 +3164,275 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>174271673.6060606</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-15219264.41</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>174412447.1531792</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-15318493.73</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>16.48</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.92</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>6621</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
         <is>
           <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>106.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>467.073</t>
+          <t>232.177</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-5.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.61</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>117.35</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>128.22</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>127.03</t>
+          <t>126.81</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.89</t>
+          <t>-141.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>49320826.0</t>
+          <t>24628089.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>48856151.4</t>
+          <t>39488115.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>73586258.9</t>
+          <t>66316644.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>286214994.92</t>
+          <t>280411936.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-24730107</t>
+          <t>-26828529</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-18681840.35212285</t>
+          <t>-18164402.41061377</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-14063047.64</v>
+        <v>-15318493.73</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-29.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>413.715</t>
+          <t>467.073</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>-33.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>118.78</t>
+          <t>117.35</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>127.03</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.92</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-138.36</t>
+          <t>-139.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>44635158.0</t>
+          <t>49320826.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>85278381.6</t>
+          <t>48856151.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>72239823.7</t>
+          <t>73586258.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>286227361.02</t>
+          <t>286214994.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>13038557</t>
+          <t>-24730107</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-19521620.84610226</t>
+          <t>-18681840.35212285</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-14412951.9</v>
+        <v>-14063047.64</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>251.273</t>
+          <t>413.715</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,275 +4457,275 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>118.78</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>129.02</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>127.27</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-15.92</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-6.05</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-5.22</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-138.36</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>174271673.6060606</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>44635158.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>85278381.6</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>72239823.7</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>286227361.02</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>13038557</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-19521620.84610226</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-14412951.9</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-28.33</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>6429</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>110.5</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>111.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>120.38</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>129.3</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-17.81</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-5.01</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-136.84</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>174412447.1531792</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>27562773.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>89666018.6</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>73099289.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>289232531.04</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>16566729</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-20450469.74495029</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-13896031</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-26.67</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>16.48</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>28.92</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>6621</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>460.487</t>
+          <t>251.273</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-9.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>121.88</t>
+          <t>120.38</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>129.49</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>127.69</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-17.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.20</t>
+          <t>-136.84</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>51293733.0</t>
+          <t>27562773.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>92108454.2</t>
+          <t>89666018.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>75715057.4</t>
+          <t>73099289.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>289684789.64</t>
+          <t>289232531.04</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>16393396</t>
+          <t>16566729</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-21642185.88004575</t>
+          <t>-20450469.74495029</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-10832101.64</v>
+        <v>-13896031</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>110.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>110.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>647.681</t>
+          <t>460.487</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,102 +5213,102 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>-1.65</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-17.54</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>-1.36</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-18.28</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-2.28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.75</t>
+          <t>-8.27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>123.08</t>
+          <t>121.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>129.67</t>
+          <t>129.49</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>127.96</t>
+          <t>127.69</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.13</t>
+          <t>-22.93</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-133.18</t>
+          <t>-135.20</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>174412447.1531792</t>
+          <t>174271673.6060606</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>71468267.0</t>
+          <t>51293733.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>93145173.8</t>
+          <t>92108454.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>75609500.8</t>
+          <t>75715057.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>290466928.82</t>
+          <t>289684789.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>17535673</t>
+          <t>16393396</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-23607655.74114843</t>
+          <t>-21642185.88004575</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-8610801.789999999</v>
+        <v>-10832101.64</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-27.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>112.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>110.5</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>109.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>109.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>110.48</t>
+          <t>109.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>123.41</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>39870339.6</t>
+          <t>32813600.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>152890945.5</t>
+          <t>135685366.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-9431051.609999999</v>
+        <v>-10072260.84</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-11466828.86</v>
+        <v>-9431051.609999999</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-14203567.65</v>
+        <v>-11466828.86</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,127 +2171,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-5.94</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-8.46</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-13742472.04</v>
+        <v>-14203567.65</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-13024441.49</v>
+        <v>-13742472.04</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-15219264.41</v>
+        <v>-13024441.49</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,275 +3595,275 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>174064964.8357349</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-15219264.41</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>16.08</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>28.46</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>6461</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>174271673.6060606</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-15318493.73</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>6429</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
         <is>
           <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>106.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>467.073</t>
+          <t>232.177</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.61</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>117.35</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>128.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>127.03</t>
+          <t>126.81</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.89</t>
+          <t>-141.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>49320826.0</t>
+          <t>24628089.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>48856151.4</t>
+          <t>39488115.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>73586258.9</t>
+          <t>66316644.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>286214994.92</t>
+          <t>280411936.8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-24730107</t>
+          <t>-26828529</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-18681840.35212285</t>
+          <t>-18164402.41061377</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-14063047.64</v>
+        <v>-15318493.73</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-29.00</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>413.715</t>
+          <t>467.073</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>-33.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>118.78</t>
+          <t>117.35</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>127.03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.92</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-138.36</t>
+          <t>-139.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>44635158.0</t>
+          <t>49320826.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>85278381.6</t>
+          <t>48856151.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>72239823.7</t>
+          <t>73586258.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>286227361.02</t>
+          <t>286214994.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>13038557</t>
+          <t>-24730107</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-19521620.84610226</t>
+          <t>-18681840.35212285</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-14412951.9</v>
+        <v>-14063047.64</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>251.273</t>
+          <t>413.715</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.45</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,275 +4888,275 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>118.78</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>129.02</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>127.27</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-15.92</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-6.05</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-5.22</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-138.36</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>174064964.8357349</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>44635158.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>85278381.6</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>72239823.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>286227361.02</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>13038557</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-19521620.84610226</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-14412951.9</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-28.33</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>16.08</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>28.46</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>6461</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>110.5</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>111.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>120.38</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>129.3</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-17.81</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-5.01</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-136.84</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>174271673.6060606</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>27562773.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>89666018.6</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>73099289.0</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>289232531.04</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>16566729</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-20450469.74495029</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-13896031</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-26.67</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>6429</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>460.487</t>
+          <t>251.273</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5319,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.27</t>
+          <t>-7.79</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,37 +5359,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>121.88</t>
+          <t>120.38</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>129.49</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>127.69</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-22.93</t>
+          <t>-17.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.89</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.20</t>
+          <t>-136.84</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>174271673.6060606</t>
+          <t>174064964.8357349</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>51293733.0</t>
+          <t>27562773.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>92108454.2</t>
+          <t>89666018.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>75715057.4</t>
+          <t>73099289.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>289684789.64</t>
+          <t>289232531.04</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16393396</t>
+          <t>16566729</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-21642185.88004575</t>
+          <t>-20450469.74495029</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-10832101.64</v>
+        <v>-13896031</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.08</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>110.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>110.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,67 +1014,67 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>109.55</t>
+          <t>108.8</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>123.41</t>
+          <t>122.72</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>32813600.0</t>
+          <t>32673934.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>135685366.26</t>
+          <t>127360637.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-10072260.84</v>
+        <v>-10255415.66</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>110.48</t>
+          <t>109.55</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>123.41</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39870339.6</t>
+          <t>32813600.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>152890945.5</t>
+          <t>135685366.26</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-9431051.609999999</v>
+        <v>-10072260.84</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-11466828.86</v>
+        <v>-9431051.609999999</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-14203567.65</v>
+        <v>-11466828.86</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,127 +2602,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-3.88</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-7.92</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-13742472.04</v>
+        <v>-14203567.65</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-13024441.49</v>
+        <v>-13742472.04</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,37 +3600,37 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-15219264.41</v>
+        <v>-13024441.49</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,270 +4031,270 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>173859250.4827338</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-15219264.41</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>28.82</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>6589</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>174064964.8357349</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-15318493.73</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.46</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>6461</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
         <is>
           <t>106.0</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>106.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>467.073</t>
+          <t>232.177</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.61</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>117.35</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>128.22</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>127.03</t>
+          <t>126.81</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.89</t>
+          <t>-141.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>49320826.0</t>
+          <t>24628089.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>48856151.4</t>
+          <t>39488115.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>73586258.9</t>
+          <t>66316644.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>286214994.92</t>
+          <t>280411936.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-24730107</t>
+          <t>-26828529</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-18681840.35212285</t>
+          <t>-18164402.41061377</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-14063047.64</v>
+        <v>-15318493.73</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-29.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>413.715</t>
+          <t>467.073</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>-33.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>118.78</t>
+          <t>117.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>127.03</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.92</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-138.36</t>
+          <t>-139.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>174064964.8357349</t>
+          <t>173859250.4827338</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44635158.0</t>
+          <t>49320826.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>85278381.6</t>
+          <t>48856151.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>72239823.7</t>
+          <t>73586258.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>286227361.02</t>
+          <t>286214994.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>13038557</t>
+          <t>-24730107</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-19521620.84610226</t>
+          <t>-18681840.35212285</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-14412951.9</v>
+        <v>-14063047.64</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>251.273</t>
+          <t>413.715</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,270 +5324,270 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.79</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>118.78</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>129.02</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>127.27</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-15.92</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-6.05</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-5.22</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-138.36</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>173859250.4827338</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>44635158.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>85278381.6</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>72239823.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>286227361.02</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>13038557</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-19521620.84610226</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-14412951.9</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-28.33</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>28.82</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>6589</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>110.5</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>111.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>120.38</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>129.3</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-17.81</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-5.01</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-136.84</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>174064964.8357349</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>27562773.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>89666018.6</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>73099289.0</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>289232531.04</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>16566729</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-20450469.74495029</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-13896031</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-26.67</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2.98</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>28.46</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>6461</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>122.72</t>
+          <t>122.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>32673934.4</t>
+          <t>37832948.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>127360637.74</t>
+          <t>123228555.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-10255415.66</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-12526934.04448037</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-8442269.669079557</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>43195246</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-31.33</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-34.00</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,72 +1450,72 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>109.55</t>
+          <t>108.8</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>123.41</t>
+          <t>122.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,180 +1540,180 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>32813600.0</t>
+          <t>32673934.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>135685366.26</t>
+          <t>127360637.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-10072260.84</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-13269600.29455325</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-10255415.66290016</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>20728993</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-32.67</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-31.33</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1713,15 +1723,20 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>110.48</t>
+          <t>109.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>123.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>39870339.6</t>
+          <t>32813600.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>152890945.5</t>
+          <t>135685366.26</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-9431051.609999999</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-13817633.86394472</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-10072260.84468315</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>20543858</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-33.00</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-32.67</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-11466828.86</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-14498610.77653773</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-9431051.609920166</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>51237586</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-31.00</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-33.00</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-14203567.65</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-15419985.1704682</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-11466828.85990447</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>53459061</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-28.67</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-31.00</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>103.5</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,127 +3063,127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-8.08</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.76</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-5.83</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-13742472.04</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-16138740.86329797</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-14203567.65059974</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>17400174</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-27.33</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-28.67</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-10.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-13024441.49</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-16490590.53833401</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-13742472.04264299</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>21427321</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-26.67</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-27.33</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,42 +4066,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4071,32 +4111,32 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-15219264.41</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-16990248.44664147</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-13024441.49403896</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>55827556</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-29.33</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-26.67</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>106.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,288 +4502,293 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>173702545.9116379</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-15219264.40696038</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>32562479</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>28.48</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>173859250.4827338</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-15318493.73</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>6589</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>106.5</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>467.073</t>
+          <t>232.177</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.61</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>117.35</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>128.22</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>127.03</t>
+          <t>126.81</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.89</t>
+          <t>-141.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49320826.0</t>
+          <t>24628089.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>48856151.4</t>
+          <t>39488115.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>73586258.9</t>
+          <t>66316644.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>286214994.92</t>
+          <t>280411936.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-24730107</t>
+          <t>-26828529</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-18681840.35212285</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-14063047.64</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-18164402.41061377</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-15318493.73231383</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>24628089</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-29.67</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-29.00</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>107.5</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>413.715</t>
+          <t>467.073</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-6.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>-33.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>118.78</t>
+          <t>117.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>129.02</t>
+          <t>128.65</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>127.03</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.92</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-5.43</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-138.36</t>
+          <t>-139.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173859250.4827338</t>
+          <t>173702545.9116379</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44635158.0</t>
+          <t>49320826.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>85278381.6</t>
+          <t>48856151.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>72239823.7</t>
+          <t>73586258.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>286227361.02</t>
+          <t>286214994.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>13038557</t>
+          <t>-24730107</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-19521620.84610226</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-14412951.9</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-18681840.35212285</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-14063047.6352361</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>49320826</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-28.33</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-29.67</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>28.82</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>28.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>6333</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>110.5</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>107.18</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>122.02</t>
+          <t>121.38</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>37832948.8</t>
+          <t>30919847.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>123228555.26</t>
+          <t>119381609.48</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>43195246</v>
+        <v>18893555</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>122.72</t>
+          <t>122.02</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>32673934.4</t>
+          <t>37832948.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>127360637.74</t>
+          <t>123228555.26</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>20728993</v>
+        <v>43195246</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>109.55</t>
+          <t>108.8</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>123.41</t>
+          <t>122.72</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>32813600.0</t>
+          <t>32673934.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>135685366.26</t>
+          <t>127360637.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>20543858</v>
+        <v>20728993</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>110.48</t>
+          <t>109.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>123.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>39870339.6</t>
+          <t>32813600.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>152890945.5</t>
+          <t>135685366.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>51237586</v>
+        <v>20543858</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>53459061</v>
+        <v>51237586</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-14203567.65059974</t>
+          <t>-11466828.85990447</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>17400174</v>
+        <v>53459061</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,127 +3499,127 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-3.88</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-10.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.76</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-13742472.04264299</t>
+          <t>-14203567.65059974</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>21427321</v>
+        <v>17400174</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13024441.49403896</t>
+          <t>-13742472.04264299</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>55827556</v>
+        <v>21427321</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,42 +4502,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4547,32 +4547,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-15219264.40696038</t>
+          <t>-13024441.49403896</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>32562479</v>
+        <v>55827556</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,280 +4938,280 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>173493991.8034433</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-15219264.40696038</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>32562479</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>28.89</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>6589</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>173702545.9116379</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-15318493.73231383</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>24628089</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>15.76</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>28.48</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>6333</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>106.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>467.073</t>
+          <t>232.177</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.57</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.61</t>
+          <t>-40.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>117.35</t>
+          <t>115.9</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>128.65</t>
+          <t>128.22</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>127.03</t>
+          <t>126.81</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-11.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.89</t>
+          <t>-141.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173702545.9116379</t>
+          <t>173493991.8034433</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>49320826.0</t>
+          <t>24628089.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>48856151.4</t>
+          <t>39488115.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>73586258.9</t>
+          <t>66316644.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>286214994.92</t>
+          <t>280411936.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-24730107</t>
+          <t>-26828529</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-18681840.35212285</t>
+          <t>-18164402.41061377</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-14063047.6352361</t>
+          <t>-15318493.73231383</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>49320826</v>
+        <v>24628089</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-29.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>107.18</t>
+          <t>106.78</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>121.38</t>
+          <t>120.78</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>30919847.6</t>
+          <t>23892723.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>119381609.48</t>
+          <t>114373076.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>18893555</v>
+        <v>16101964</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>107.18</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>122.02</t>
+          <t>121.38</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>37832948.8</t>
+          <t>30919847.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>123228555.26</t>
+          <t>119381609.48</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>43195246</v>
+        <v>18893555</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>122.72</t>
+          <t>122.02</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>32673934.4</t>
+          <t>37832948.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>127360637.74</t>
+          <t>123228555.26</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>20728993</v>
+        <v>43195246</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,72 +2322,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>109.55</t>
+          <t>108.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>123.41</t>
+          <t>122.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>32813600.0</t>
+          <t>32673934.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>135685366.26</t>
+          <t>127360637.74</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>20543858</v>
+        <v>20728993</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>110.48</t>
+          <t>109.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>123.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>39870339.6</t>
+          <t>32813600.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>152890945.5</t>
+          <t>135685366.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>51237586</v>
+        <v>20543858</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>53459061</v>
+        <v>51237586</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-14203567.65059974</t>
+          <t>-11466828.85990447</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>17400174</v>
+        <v>53459061</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,127 +3935,127 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-5.83</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.81</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-13742472.04264299</t>
+          <t>-14203567.65059974</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>21427321</v>
+        <v>17400174</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.8</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-13024441.49403896</t>
+          <t>-13742472.04264299</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>55827556</v>
+        <v>21427321</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,32 +4983,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173493991.8034433</t>
+          <t>173280036.1504298</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-15219264.40696038</t>
+          <t>-13024441.49403896</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>32562479</v>
+        <v>55827556</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>232.177</t>
+          <t>304.659</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-40.46</t>
+          <t>-44.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.52</t>
+          <t>-20.90</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,280 +5374,280 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>155</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>107.1</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>114.58</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>127.73</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>126.61</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-9.04</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-5.72</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-142.07</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>173280036.1504298</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>32562479.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>35741865.0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>63925159.6</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>274452338.02</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-28183294</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-17711304.25620556</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-15219264.40696038</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>32562479</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-29.33</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>16.72</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>6717</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>115.9</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>128.22</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>126.81</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-5.59</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-141.12</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>173493991.8034433</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>24628089.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>39488115.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>66316644.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>280411936.8</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-26828529</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-18164402.41061377</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-15318493.73231383</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>24628089</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-29.00</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>6589</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>106.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>106.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>106.78</t>
+          <t>106.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>120.78</t>
+          <t>120.39</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23892723.2</t>
+          <t>39907180.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>114373076.4</t>
+          <t>112974230.9</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>16101964</v>
+        <v>100616146</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>107.18</t>
+          <t>106.78</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>121.38</t>
+          <t>120.78</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30919847.6</t>
+          <t>23892723.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>119381609.48</t>
+          <t>114373076.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>18893555</v>
+        <v>16101964</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>107.8</t>
+          <t>107.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>122.02</t>
+          <t>121.38</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>37832948.8</t>
+          <t>30919847.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>123228555.26</t>
+          <t>119381609.48</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>43195246</v>
+        <v>18893555</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,27 +2139,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>108.8</t>
+          <t>107.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>122.72</t>
+          <t>122.02</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>32673934.4</t>
+          <t>37832948.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>127360637.74</t>
+          <t>123228555.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>20728993</v>
+        <v>43195246</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,72 +2758,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>109.55</t>
+          <t>108.8</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>123.41</t>
+          <t>122.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32813600.0</t>
+          <t>32673934.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>135685366.26</t>
+          <t>127360637.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>20543858</v>
+        <v>20728993</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>110.48</t>
+          <t>109.55</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>124.17</t>
+          <t>123.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39870339.6</t>
+          <t>32813600.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>152890945.5</t>
+          <t>135685366.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>51237586</v>
+        <v>20543858</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>9.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>111.48</t>
+          <t>110.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>125.16</t>
+          <t>124.17</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36135318.2</t>
+          <t>39870339.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>214011460.78</t>
+          <t>152890945.5</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>53459061</v>
+        <v>51237586</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>112.32</t>
+          <t>111.48</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>125.99</t>
+          <t>125.16</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30369123.8</t>
+          <t>36135318.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>232296578.54</t>
+          <t>214011460.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-14203567.65059974</t>
+          <t>-11466828.85990447</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>17400174</v>
+        <v>53459061</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4371,127 +4371,127 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-3.81</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.32</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>126.49</t>
+          <t>125.99</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36753254.2</t>
+          <t>30369123.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>239918216.68</t>
+          <t>232296578.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-13742472.04264299</t>
+          <t>-14203567.65059974</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>21427321</v>
+        <v>17400174</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,27 +4755,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>127.06</t>
+          <t>126.49</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>41394821.6</t>
+          <t>36753254.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>258668693.84</t>
+          <t>239918216.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-13024441.49403896</t>
+          <t>-13742472.04264299</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>55827556</v>
+        <v>21427321</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>304.659</t>
+          <t>508.508</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-44.09</t>
+          <t>-36.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.90</t>
+          <t>-17.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,42 +5374,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>914</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>34.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.3</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>114.58</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>127.73</t>
+          <t>127.06</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>126.61</t>
+          <t>126.41</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-142.07</t>
+          <t>-142.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173280036.1504298</t>
+          <t>173248053.5793991</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32562479.0</t>
+          <t>55827556.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>35741865.0</t>
+          <t>41394821.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>63925159.6</t>
+          <t>65530420.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>274452338.02</t>
+          <t>258668693.84</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-28183294</t>
+          <t>-24135598</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-17711304.25620556</t>
+          <t>-16990248.44664147</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-15219264.40696038</t>
+          <t>-13024441.49403896</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>32562479</v>
+        <v>55827556</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-29.33</t>
+          <t>-26.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.72</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>104.1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>106.6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>120.39</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>120.39</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>100616146.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>39907180.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>39907180.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>36360390.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>112974230.9</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>112974230.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-2610721.237659656</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>100616146</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>100616146.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>102.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>106.78</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>120.78</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>120.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>16101964.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>23892723.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>23892723.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>31881531.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>114373076.4</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>114373076.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9014048.464080215</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>16101964</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>16101964.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>101.3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>107.18</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>121.38</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>107.18</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>121.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>18893555.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>30919847.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>30919847.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>33527582.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>119381609.48</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>119381609.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-8784637.556678154</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>18893555</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18893555.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>101.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>107.8</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>122.02</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>122.02</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>43195246.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>37832948.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>37832948.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>34101036.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>123228555.26</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>123228555.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-8442269.669079557</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>43195246</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>43195246.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>103.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>108.8</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>122.72</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>122.72</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>20728993.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>32673934.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>32673934.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>34713594.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>127360637.74</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>127360637.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-10255415.66290016</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>20728993</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>20728993.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>104.2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>109.55</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>123.41</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>109.55</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>123.41</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>20543858.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>32813600.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>32813600</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>37104210.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>135685366.26</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>135685366.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-10072260.84468315</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>20543858</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>20543858.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>106.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>110.48</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>124.17</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>110.48</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>124.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>51237586.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>39870339.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>39870339.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>37806102.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>152890945.5</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>152890945.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-9431051.609920166</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>51237586</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>51237586.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>107.1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>111.48</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>125.16</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>111.48</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>125.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>53459061.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>36135318.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>36135318.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>37811717.0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>214011460.78</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>214011460.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-11466828.85990447</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>53459061</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>53459061.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>107.7</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>112.32</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>125.99</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>112.32</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>125.99</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>17400174.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>30369123.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>30369123.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>39612637.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>232296578.54</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>232296578.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-14203567.65059974</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>17400174</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>17400174.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>107.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>113.1</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>126.49</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>126.49</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>21427321.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>36753254.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>36753254.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>61015817.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>239918216.68</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>239918216.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-13742472.04264299</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>21427321</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>21427321.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>107.1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>113.78</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>127.06</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>113.78</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>127.06</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>55827556.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>41394821.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>41394821.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>65530420.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>258668693.84</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>258668693.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13024441.49403896</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>55827556</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>55827556.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,27 +1261,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN4" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,27 +2121,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,14 +2156,14 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,27 +2551,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>109.55</v>
+        <v>108.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>123.41</v>
+        <v>122.72</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>32813600</v>
+        <v>32673934.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>135685366.26</v>
+        <v>127360637.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>110.48</v>
+        <v>109.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>124.17</v>
+        <v>123.41</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>39870339.6</v>
+        <v>32813600</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>152890945.5</v>
+        <v>135685366.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,14 +3876,14 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>111.48</v>
+        <v>110.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>125.16</v>
+        <v>124.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>36135318.2</v>
+        <v>39870339.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>214011460.78</v>
+        <v>152890945.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>112.32</v>
+        <v>111.48</v>
       </c>
       <c r="AN10" t="n">
-        <v>125.99</v>
+        <v>125.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>30369123.8</v>
+        <v>36135318.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>232296578.54</v>
+        <v>214011460.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14203567.65059974</t>
+          <t>-11466828.85990447</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,127 +4753,127 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>113.1</v>
+        <v>112.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>126.49</v>
+        <v>125.99</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>36753254.2</v>
+        <v>30369123.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>239918216.68</v>
+        <v>232296578.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-13742472.04264299</t>
+          <t>-14203567.65059974</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,27 +5131,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>508.508</t>
+          <t>195.902</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-39.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-17.91</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>393</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>54.72</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.46</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>107.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>113.78</v>
+        <v>113.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>127.06</v>
+        <v>126.49</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>126.41</t>
+          <t>126.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.70</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-142.23</t>
+          <t>-141.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173248053.5793991</t>
+          <t>173091865.6842857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>41394821.6</v>
+        <v>36753254.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>65530420.1</t>
+          <t>61015817.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>258668693.84</v>
+        <v>239918216.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-24135598</t>
+          <t>-24262563</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16990248.44664147</t>
+          <t>-16490590.53833401</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-13024441.49403896</t>
+          <t>-13742472.04264299</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>55827556.0</t>
+          <t>21427321.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-26.67</t>
+          <t>-27.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-6.4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-5.13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15.09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-19.40</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-2.31</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>9.75</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-17.54</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN4" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN5" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>109.55</v>
+        <v>108.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>123.41</v>
+        <v>122.72</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>32813600</v>
+        <v>32673934.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>135685366.26</v>
+        <v>127360637.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>110.48</v>
+        <v>109.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>124.17</v>
+        <v>123.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>39870339.6</v>
+        <v>32813600</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>152890945.5</v>
+        <v>135685366.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>111.48</v>
+        <v>110.48</v>
       </c>
       <c r="AN10" t="n">
-        <v>125.16</v>
+        <v>124.17</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>36135318.2</v>
+        <v>39870339.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>214011460.78</v>
+        <v>152890945.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>112.32</v>
+        <v>111.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>125.99</v>
+        <v>125.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>30369123.8</v>
+        <v>36135318.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>232296578.54</v>
+        <v>214011460.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-14203567.65059974</t>
+          <t>-11466828.85990447</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,127 +5183,127 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>161.669</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-5.42</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-5.13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-23.33</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-20.15</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>195.902</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-39.76</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-18.66</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-1.37</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>113.1</v>
+        <v>112.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>126.49</v>
+        <v>125.99</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>126.24</t>
+          <t>126.01</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.70</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.91</t>
+          <t>-141.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173091865.6842857</t>
+          <t>173145678.4985735</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>36753254.2</v>
+        <v>30369123.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>61015817.9</t>
+          <t>39612637.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>239918216.68</v>
+        <v>232296578.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-24262563</t>
+          <t>-9243513</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16490590.53833401</t>
+          <t>-16138740.86329797</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-13742472.04264299</t>
+          <t>-14203567.65059974</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>21427321.0</t>
+          <t>17400174.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-27.33</t>
+          <t>-28.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6493</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN2" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN3" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-10.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,68 +4024,68 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>109.55</v>
+        <v>108.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>123.41</v>
+        <v>122.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>32813600</v>
+        <v>32673934.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>135685366.26</v>
+        <v>127360637.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>110.48</v>
+        <v>109.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>124.17</v>
+        <v>123.41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>39870339.6</v>
+        <v>32813600</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>152890945.5</v>
+        <v>135685366.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>111.48</v>
+        <v>110.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>125.16</v>
+        <v>124.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>36135318.2</v>
+        <v>39870339.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>214011460.78</v>
+        <v>152890945.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>161.669</t>
+          <t>515.622</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.33</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-20.15</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-10.93</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>107.7</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>112.32</v>
+        <v>111.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>125.99</v>
+        <v>125.16</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>126.01</t>
+          <t>125.74</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.44</t>
+          <t>-141.21</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173145678.4985735</t>
+          <t>173145391.5064102</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>30369123.8</v>
+        <v>36135318.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>39612637.6</t>
+          <t>37811717.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>232296578.54</v>
+        <v>214011460.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9243513</t>
+          <t>-1676398</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16138740.86329797</t>
+          <t>-15419985.1704682</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-14203567.65059974</t>
+          <t>-11466828.85990447</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>17400174.0</t>
+          <t>53459061.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-28.67</t>
+          <t>-31.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>15.62</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-10.09</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN4" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.03</t>
+          <t>-11.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN7" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>109.55</v>
+        <v>108.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>123.41</v>
+        <v>122.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>32813600</v>
+        <v>32673934.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>135685366.26</v>
+        <v>127360637.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>110.48</v>
+        <v>109.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>124.17</v>
+        <v>123.41</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>39870339.6</v>
+        <v>32813600</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>152890945.5</v>
+        <v>135685366.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>515.622</t>
+          <t>506.238</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>653</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-11.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>111.48</v>
+        <v>110.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>125.16</v>
+        <v>124.17</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>125.74</t>
+          <t>125.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.21</t>
+          <t>-141.42</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173145391.5064102</t>
+          <t>173036725.5640114</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>36135318.2</v>
+        <v>39870339.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>37811717.0</t>
+          <t>37806102.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>214011460.78</v>
+        <v>152890945.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1676398</t>
+          <t>2064237</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-15419985.1704682</t>
+          <t>-14498610.77653773</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-11466828.85990447</t>
+          <t>-9431051.609920166</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>53459061.0</t>
+          <t>51237586.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-31.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.62</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【y】創高</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-11.62</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-9.95</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>109.55</v>
+        <v>108.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>123.41</v>
+        <v>122.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>32813600</v>
+        <v>32673934.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>135685366.26</v>
+        <v>127360637.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>506.238</t>
+          <t>203.608</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>-11.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-24.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.03</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>110.48</v>
+        <v>109.55</v>
       </c>
       <c r="AN12" t="n">
-        <v>124.17</v>
+        <v>123.41</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>125.44</t>
+          <t>125.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.42</t>
+          <t>-141.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173036725.5640114</t>
+          <t>173009868.2727273</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>39870339.6</v>
+        <v>32813600</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>37806102.3</t>
+          <t>37104210.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>152890945.5</v>
+        <v>135685366.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2064237</t>
+          <t>-4290610</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14498610.77653773</t>
+          <t>-13817633.86394472</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-9431051.609920166</t>
+          <t>-10072260.84468315</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>51237586.0</t>
+          <t>20543858.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-32.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AN2" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.95</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN9" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-5.55</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>203.608</t>
+          <t>202.376</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.56</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.63</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,68 +5314,68 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>674</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>104.2</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>109.55</v>
+        <v>108.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>123.41</v>
+        <v>122.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>125.14</t>
+          <t>124.81</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.72</t>
+          <t>-141.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>173009868.2727273</t>
+          <t>172907037.5574468</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>32813600</v>
+        <v>32673934.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>37104210.8</t>
+          <t>34713594.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>135685366.26</v>
+        <v>127360637.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4290610</t>
+          <t>-2039659</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13817633.86394472</t>
+          <t>-13269600.29455325</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-10072260.84468315</t>
+          <t>-10255415.66290016</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20543858.0</t>
+          <t>20728993.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-32.67</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】;【y】創高</t>
+          <t>【y】創高</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>356.655</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>673.665</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>99.2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.83</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-3.98</t>
-        </is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-4.15</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.12</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-4.14</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-4.41</t>
-        </is>
+          <t>5.82</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-4.34</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1293,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>3004</t>
@@ -1313,12 +1301,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1316,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1326,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1401,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1411,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1432,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.87</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-2.67</t>
-        </is>
+          <t>11.83</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-3.98</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AN3" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.31</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-4.15</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-4.47</t>
-        </is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-4.41</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1500,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1510,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1566,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1611,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1636,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1651,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1676,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1711,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>3004</t>
@@ -1743,12 +1719,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1734,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1744,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1829,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1850,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.67</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-4.27</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.20</t>
-        </is>
+          <t>8.87</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.67</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.13</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-4.56</t>
-        </is>
+          <t>7.31</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-4.47</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1918,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1928,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1984,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2029,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2039,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2054,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2069,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2094,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2129,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>3004</t>
@@ -2173,12 +2137,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2152,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2162,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2237,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2247,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2268,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-6.23</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
+          <t>9.67</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.05</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-4.12</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-4.64</t>
-        </is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-4.56</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2336,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2346,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2402,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2447,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2472,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2487,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2512,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2547,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>3004</t>
@@ -2603,12 +2555,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2570,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2580,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2655,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2665,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2686,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-3.88</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.6</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.48</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-3.84</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-4.76</t>
-        </is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-4.64</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2754,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2764,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2820,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2865,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2890,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2905,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2930,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2965,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>3004</t>
@@ -3033,12 +2973,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2988,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +2998,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3073,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3083,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3104,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>79.42</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2.76</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.21</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN7" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>24.75</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-3.76</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-5.00</t>
-        </is>
+          <t>19.48</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-4.76</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3172,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3182,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3238,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3283,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3308,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3323,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3348,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3451,11 +3383,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>3004</t>
@@ -3463,12 +3391,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3406,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3416,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3491,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3501,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3522,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>65.45</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>6.15</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
+          <t>79.42</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.97</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.54</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-4.27</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-5.31</t>
-        </is>
+          <t>24.75</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-5</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3590,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3600,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3656,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3701,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3726,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3741,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3766,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3881,11 +3801,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>3004</t>
@@ -3893,12 +3809,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3824,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3834,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3909,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3919,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3940,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>32.12</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-4.28</t>
-        </is>
+          <t>65.45</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-2.35</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>8.15</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-5.11</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-5.56</t>
-        </is>
+          <t>19.54</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-5.31</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4008,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4018,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4074,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4119,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4144,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4159,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4184,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4311,11 +4219,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>3004</t>
@@ -4323,12 +4227,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4242,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4252,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4327,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4337,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4358,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20.89</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-5.48</t>
-        </is>
+          <t>32.12</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-4.28</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN10" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.22</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-5.55</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-5.68</t>
-        </is>
+          <t>8.15</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-5.56</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4426,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4436,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4492,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4547,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4562,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4577,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4602,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4741,11 +4637,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>3004</t>
@@ -4753,12 +4645,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4660,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4670,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4745,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4755,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4776,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.53</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-2.37</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-5.94</t>
-        </is>
+          <t>20.89</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-5.48</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.11</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-5.83</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-5.71</t>
-        </is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-5.55</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-5.68</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4844,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4854,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4910,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4955,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +4965,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +4980,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +4995,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5020,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5067,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>202.376</t>
+          <t>430.43</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5082,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5092,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5167,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5177,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5198,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5216,48 @@
           <t>10.53</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-5.33</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-5.94</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.34</t>
+          <t>-11.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>108.8</v>
+        <v>107.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>122.72</v>
+        <v>122.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>124.81</t>
+          <t>124.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-5.69</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-5.68</t>
-        </is>
+          <t>-2.11</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-5.71</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5266,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.75</t>
+          <t>-141.97</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5276,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>172907037.5574468</t>
+          <t>172737598.8526912</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>32673934.4</v>
+        <v>37832948.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>34713594.3</t>
+          <t>34101036.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>127360637.74</v>
+        <v>123228555.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2039659</t>
+          <t>3731912</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13269600.29455325</t>
+          <t>-12526934.04448037</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-10255415.66290016</t>
+          <t>-8442269.669079557</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20728993.0</t>
+          <t>43195246.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5332,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5377,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5387,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5402,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.78</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5417,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5442,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【y】創高</t>
+          <t>【d2】;【y】創高</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1293,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>3004</t>
@@ -1301,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>673.665</t>
+          <t>356.655</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1316,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1326,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1401,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1411,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1432,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1510,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1566,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1621,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1636,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1651,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1676,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1711,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>3004</t>
@@ -1719,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1744,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1819,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1829,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1850,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AN4" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="AR4" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1928,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1984,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2029,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2054,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2069,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2094,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2129,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>3004</t>
@@ -2137,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2152,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2162,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2237,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2247,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2268,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2336,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2346,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2402,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2447,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2457,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2472,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2487,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2512,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2547,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>3004</t>
@@ -2555,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2570,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2580,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2655,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2665,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2686,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-6.23</v>
+        <v>-4.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.64</v>
+        <v>-4.56</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2754,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2764,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2820,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2865,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2905,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2930,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2965,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>3004</t>
@@ -2973,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2988,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2998,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3073,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3083,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3104,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-3.88</v>
+        <v>-6.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.84</v>
+        <v>-4.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.76</v>
+        <v>-4.64</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3172,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3182,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3238,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3308,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3323,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3348,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3383,7 +3403,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>3004</t>
@@ -3391,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3406,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3416,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3491,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3501,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3522,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.76</v>
+        <v>-3.88</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.97</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.76</v>
+        <v>-3.84</v>
       </c>
       <c r="AR8" t="n">
-        <v>-5</v>
+        <v>-4.76</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3590,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3600,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3656,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3701,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3726,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3741,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3766,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3801,7 +3825,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>3004</t>
@@ -3809,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3824,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3834,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-8.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3909,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3919,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3940,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>6.15</v>
+        <v>2.76</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.35</v>
+        <v>-0.97</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-4.27</v>
+        <v>-3.76</v>
       </c>
       <c r="AR9" t="n">
-        <v>-5.31</v>
+        <v>-5</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4008,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4018,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4074,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4119,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4144,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4159,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4184,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4219,7 +4247,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>3004</t>
@@ -4227,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4242,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4252,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-10.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4327,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4337,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4358,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.74</v>
+        <v>6.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.28</v>
+        <v>-2.35</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-5.11</v>
+        <v>-4.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-5.56</v>
+        <v>-5.31</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4426,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4436,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4492,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4537,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4562,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4577,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4602,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4637,7 +4669,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>3004</t>
@@ -4645,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4660,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4670,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4745,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4755,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4776,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.48</v>
+        <v>-4.28</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN11" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-5.55</v>
+        <v>-5.11</v>
       </c>
       <c r="AR11" t="n">
-        <v>-5.68</v>
+        <v>-5.56</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4844,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4854,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4910,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4965,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -4980,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -4995,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5020,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5057,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5067,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>430.43</t>
+          <t>185.537</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5082,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5092,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>-7.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5167,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5177,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5198,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>223</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.37</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.94</v>
+        <v>-5.48</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.65</t>
+          <t>-11.7</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>101.4</t>
+          <t>101.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>107.8</v>
+        <v>107.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>122.02</v>
+        <v>121.38</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>124.49</t>
+          <t>124.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-5.83</v>
+        <v>-5.55</v>
       </c>
       <c r="AR12" t="n">
-        <v>-5.71</v>
+        <v>-5.68</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5266,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.97</t>
+          <t>-141.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5276,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>172737598.8526912</t>
+          <t>172540175.2340877</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>37832948.8</v>
+        <v>30919847.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>34101036.3</t>
+          <t>33527582.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>123228555.26</v>
+        <v>119381609.48</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3731912</t>
+          <t>-2607735</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12526934.04448037</t>
+          <t>-11951196.12328003</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-8442269.669079557</t>
+          <t>-8784637.556678154</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>43195246.0</t>
+          <t>18893555.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5332,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-31.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5377,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5387,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5402,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5417,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5442,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>223.045</t>
+          <t>191.359</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.67999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>103.12</v>
+        <v>102.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>114.79</v>
+        <v>114.05</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>120.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.97</v>
+        <v>-3.79</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.27</v>
+        <v>-4.17</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.37</t>
+          <t>-130.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>58378540.4</v>
+        <v>49303933.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>70706106.9</t>
+          <t>71008822.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>80937019.98</v>
+        <v>79031251.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-12327566</t>
+          <t>-21704889</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>177730.2094763927</t>
+          <t>-474166.0737401107</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1253108.279772744</t>
+          <t>-4059595.631430879</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-33.33</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="AR3" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>673.665</t>
+          <t>356.655</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AN5" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,61 +2707,61 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-6.23</v>
+        <v>-4.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.64</v>
+        <v>-4.56</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-3.88</v>
+        <v>-6.23</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.84</v>
+        <v>-4.12</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.76</v>
+        <v>-4.64</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.43</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.76</v>
+        <v>-3.88</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.97</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.76</v>
+        <v>-3.84</v>
       </c>
       <c r="AR9" t="n">
-        <v>-5</v>
+        <v>-4.76</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.94</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>6.15</v>
+        <v>2.76</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.35</v>
+        <v>-0.97</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-4.27</v>
+        <v>-3.76</v>
       </c>
       <c r="AR10" t="n">
-        <v>-5.31</v>
+        <v>-5</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.74</v>
+        <v>6.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.28</v>
+        <v>-2.35</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-5.11</v>
+        <v>-4.27</v>
       </c>
       <c r="AR11" t="n">
-        <v>-5.56</v>
+        <v>-5.31</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>185.537</t>
+          <t>154.768</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.78</t>
+          <t>-25.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-21.64</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>191</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.48</v>
+        <v>-4.28</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.7</t>
+          <t>-11.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>102.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>107.18</v>
+        <v>106.78</v>
       </c>
       <c r="AN12" t="n">
-        <v>121.38</v>
+        <v>120.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>124.22</t>
+          <t>123.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-5.55</v>
+        <v>-5.11</v>
       </c>
       <c r="AR12" t="n">
-        <v>-5.68</v>
+        <v>-5.56</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-141.74</t>
+          <t>-140.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>172540175.2340877</t>
+          <t>172337002.2245763</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>30919847.6</v>
+        <v>23892723.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>33527582.9</t>
+          <t>31881531.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>119381609.48</v>
+        <v>114373076.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2607735</t>
+          <t>-7988808</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11951196.12328003</t>
+          <t>-11499327.25263391</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-8784637.556678154</t>
+          <t>-9014048.464080215</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18893555.0</t>
+          <t>16101964.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-31.33</t>
+          <t>-30.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.92</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>99.9</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>191.359</t>
+          <t>218.931</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-47.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-26.19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="AI2" t="n">
-        <v>-3.06</v>
+        <v>-2.85</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.67999999999999</t>
+          <t>99.35999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>102.82</v>
+        <v>102.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>114.05</v>
+        <v>113.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>120.98</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.79</v>
+        <v>-3.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.17</v>
+        <v>-4.08</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.67</t>
+          <t>-129.98</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>49303933.8</v>
+        <v>33101836.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>71008822.8</t>
+          <t>63121439.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>79031251.22</v>
+        <v>77659853.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-21704889</t>
+          <t>-30019602</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-474166.0737401107</t>
+          <t>-1282241.733442525</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4059595.631430879</t>
+          <t>-5726657.861805804</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-33.33</t>
+          <t>-34.07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>223.045</t>
+          <t>191.359</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.67999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>103.12</v>
+        <v>102.82</v>
       </c>
       <c r="AN3" t="n">
-        <v>114.79</v>
+        <v>114.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>120.98</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-3.97</v>
+        <v>-3.79</v>
       </c>
       <c r="AR3" t="n">
-        <v>-4.27</v>
+        <v>-4.17</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.37</t>
+          <t>-130.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>58378540.4</v>
+        <v>49303933.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>70706106.9</t>
+          <t>71008822.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>80937019.98</v>
+        <v>79031251.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-12327566</t>
+          <t>-21704889</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>177730.2094763927</t>
+          <t>-474166.0737401107</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1253108.279772744</t>
+          <t>-4059595.631430879</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-33.33</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AI4" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="AR4" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>673.665</t>
+          <t>356.655</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AN5" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AN6" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-6.23</v>
+        <v>-4.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.64</v>
+        <v>-4.56</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-3.88</v>
+        <v>-6.23</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.84</v>
+        <v>-4.12</v>
       </c>
       <c r="AR9" t="n">
-        <v>-4.76</v>
+        <v>-4.64</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.76</v>
+        <v>-3.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.97</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.76</v>
+        <v>-3.84</v>
       </c>
       <c r="AR10" t="n">
-        <v>-5</v>
+        <v>-4.76</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-9.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>6.15</v>
+        <v>2.76</v>
       </c>
       <c r="AI11" t="n">
-        <v>-2.35</v>
+        <v>-0.97</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-4.27</v>
+        <v>-3.76</v>
       </c>
       <c r="AR11" t="n">
-        <v>-5.31</v>
+        <v>-5</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>154.768</t>
+          <t>914.281</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-25.06</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>65.45</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>2.74</v>
+        <v>6.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.28</v>
+        <v>-2.35</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>102.2</t>
+          <t>104.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>106.78</v>
+        <v>106.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>120.78</v>
+        <v>120.39</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>123.96</t>
+          <t>123.78</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-5.11</v>
+        <v>-4.27</v>
       </c>
       <c r="AR12" t="n">
-        <v>-5.56</v>
+        <v>-5.31</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-140.90</t>
+          <t>-139.00</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>172337002.2245763</t>
+          <t>172139930.944993</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>23892723.2</v>
+        <v>39907180.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31881531.4</t>
+          <t>36360390.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>114373076.4</v>
+        <v>112974230.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-7988808</t>
+          <t>3546790</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11499327.25263391</t>
+          <t>-10131849.40417633</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-9014048.464080215</t>
+          <t>-2610721.237659656</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>16101964.0</t>
+          <t>100616146.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-30.00</t>
+          <t>-26.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.92</t>
+          <t>15.75</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>30.17</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>218.931</t>
+          <t>235.048</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.56</t>
+          <t>-60.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.19</t>
+          <t>-26.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.46</v>
+        <v>-1.21</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>99.35999999999999</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>102.27</v>
+        <v>101.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.34</v>
+        <v>112.68</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.7</v>
+        <v>-3.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4.08</v>
+        <v>-4</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.98</t>
+          <t>-129.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>33101836.8</v>
+        <v>24344852.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>63121439.2</t>
+          <t>61182793.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>77659853.2</v>
+        <v>76121371.45999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-30019602</t>
+          <t>-36837940</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1282241.733442525</t>
+          <t>-2106399.393916461</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5726657.861805804</t>
+          <t>-6639266.526523106</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.07</t>
+          <t>-34.73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>191.359</t>
+          <t>218.931</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-47.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-26.19</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3.06</v>
+        <v>-2.85</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>99.67999999999999</t>
+          <t>99.35999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>102.82</v>
+        <v>102.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>114.05</v>
+        <v>113.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>120.98</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-3.79</v>
+        <v>-3.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>-4.17</v>
+        <v>-4.08</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.67</t>
+          <t>-129.98</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>49303933.8</v>
+        <v>33101836.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>71008822.8</t>
+          <t>63121439.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>79031251.22</v>
+        <v>77659853.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-21704889</t>
+          <t>-30019602</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-474166.0737401107</t>
+          <t>-1282241.733442525</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-4059595.631430879</t>
+          <t>-5726657.861805804</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-33.33</t>
+          <t>-34.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>223.045</t>
+          <t>191.359</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.67999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>103.12</v>
+        <v>102.82</v>
       </c>
       <c r="AN4" t="n">
-        <v>114.79</v>
+        <v>114.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>120.98</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-3.97</v>
+        <v>-3.79</v>
       </c>
       <c r="AR4" t="n">
-        <v>-4.27</v>
+        <v>-4.17</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.37</t>
+          <t>-130.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>58378540.4</v>
+        <v>49303933.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>70706106.9</t>
+          <t>71008822.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>80937019.98</v>
+        <v>79031251.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-12327566</t>
+          <t>-21704889</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>177730.2094763927</t>
+          <t>-474166.0737401107</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1253108.279772744</t>
+          <t>-4059595.631430879</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-33.33</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>673.665</t>
+          <t>356.655</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AN6" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AN7" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="AR7" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="AR8" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-6.23</v>
+        <v>-4.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AN9" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>-4.64</v>
+        <v>-4.56</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-3.88</v>
+        <v>-6.23</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.84</v>
+        <v>-4.12</v>
       </c>
       <c r="AR10" t="n">
-        <v>-4.76</v>
+        <v>-4.64</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>393.128</t>
+          <t>1371.211</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-19.40</t>
+          <t>-24.25</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>79.42</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.76</v>
+        <v>-3.88</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.97</v>
+        <v>-0.21</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>106.12</v>
+        <v>105.82</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.84</v>
+        <v>119.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>123.56</t>
+          <t>123.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.76</v>
+        <v>-3.84</v>
       </c>
       <c r="AR11" t="n">
-        <v>-5</v>
+        <v>-4.76</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-136.72</t>
+          <t>-135.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>44283585.8</v>
+        <v>63753156.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>38478760.1</t>
+          <t>50793052.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>107346301.38</v>
+        <v>99353698.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5804825</t>
+          <t>12960103</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8944412.380183628</t>
+          <t>-6779151.431218925</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2413508.748223774</t>
+          <t>5129783.788086943</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>42611018.0</t>
+          <t>140543099.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-28.00</t>
+          <t>-32.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>111.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>914.281</t>
+          <t>393.128</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>15.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-19.40</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>235</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>65.45</t>
+          <t>79.42</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>6.15</v>
+        <v>2.76</v>
       </c>
       <c r="AI12" t="n">
-        <v>-2.35</v>
+        <v>-0.97</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>104.1</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>106.6</v>
+        <v>106.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>120.39</v>
+        <v>119.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>123.78</t>
+          <t>123.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-4.27</v>
+        <v>-3.76</v>
       </c>
       <c r="AR12" t="n">
-        <v>-5.31</v>
+        <v>-5</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-139.00</t>
+          <t>-136.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>172139930.944993</t>
+          <t>171946546.3014084</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>39907180.8</v>
+        <v>44283585.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36360390.4</t>
+          <t>38478760.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>112974230.9</v>
+        <v>107346301.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3546790</t>
+          <t>5804825</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10131849.40417633</t>
+          <t>-8944412.380183628</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2610721.237659656</t>
+          <t>-2413508.748223774</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>100616146.0</t>
+          <t>42611018.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-26.33</t>
+          <t>-28.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.75</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>613.459</t>
+          <t>272.779</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-26.57</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-1.7</v>
+        <v>-0.04</v>
       </c>
       <c r="AQ2" t="n">
         <v>-2.5</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>98.68</t>
+          <t>98.44</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>101.22</v>
+        <v>100.96</v>
       </c>
       <c r="AV2" t="n">
-        <v>111.87</v>
+        <v>111.12</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>120.05</t>
+          <t>119.73</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-3.67</v>
+        <v>-3.52</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-3.93</v>
+        <v>-3.85</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-128.90</t>
+          <t>-128.29</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>59596193.0</t>
+          <t>26801175.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>29159649.8</v>
+        <v>30098671.4</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>53088102.4</t>
+          <t>44238605.9</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>73931584</v>
+        <v>70674096.40000001</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-23928452</t>
+          <t>-14139934</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-2456836.126185026</t>
+          <t>-2872051.905051623</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-4384238.153662138</t>
+          <t>-5155738.688817903</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>59596193.0</t>
+          <t>26801175.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>235.048</t>
+          <t>613.459</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-60.21</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.94</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,12 +1556,12 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1571,51 +1571,51 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-1.21</v>
+        <v>-1.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2.57</v>
+        <v>-2.5</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.68</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>101.72</v>
+        <v>101.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>112.68</v>
+        <v>111.87</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>120.37</t>
+          <t>120.05</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AY3" t="n">
         <v>-3.67</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-4</v>
+        <v>-3.93</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-129.37</t>
+          <t>-128.90</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>23224556.0</t>
+          <t>59596193.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>24344852.8</v>
+        <v>29159649.8</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>61182793.0</t>
+          <t>53088102.4</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>76121371.45999999</v>
+        <v>73931584</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-36837940</t>
+          <t>-23928452</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-2106399.393916461</t>
+          <t>-2456836.126185026</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-6639266.526523106</t>
+          <t>-4384238.153662138</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>23224556.0</t>
+          <t>59596193.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-34.73</t>
+          <t>-35.33</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>218.931</t>
+          <t>235.048</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.56</t>
+          <t>-60.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.19</t>
+          <t>-26.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-0.46</v>
+        <v>-1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>99.35999999999999</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>102.27</v>
+        <v>101.72</v>
       </c>
       <c r="AV4" t="n">
-        <v>113.34</v>
+        <v>112.68</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.37</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-3.7</v>
+        <v>-3.67</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-4.08</v>
+        <v>-4</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-129.98</t>
+          <t>-129.37</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>33101836.8</v>
+        <v>24344852.8</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>63121439.2</t>
+          <t>61182793.0</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>77659853.2</v>
+        <v>76121371.45999999</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-30019602</t>
+          <t>-36837940</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-1282241.733442525</t>
+          <t>-2106399.393916461</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-5726657.861805804</t>
+          <t>-6639266.526523106</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-34.07</t>
+          <t>-34.73</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>191.359</t>
+          <t>218.931</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-47.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-26.19</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-3.06</v>
+        <v>-2.85</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>99.67999999999999</t>
+          <t>99.35999999999999</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>102.82</v>
+        <v>102.27</v>
       </c>
       <c r="AV5" t="n">
-        <v>114.05</v>
+        <v>113.34</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>120.98</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-3.79</v>
+        <v>-3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-4.17</v>
+        <v>-4.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-130.67</t>
+          <t>-129.98</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>49303933.8</v>
+        <v>33101836.8</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>71008822.8</t>
+          <t>63121439.2</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>79031251.22</v>
+        <v>77659853.2</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-21704889</t>
+          <t>-30019602</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-474166.0737401107</t>
+          <t>-1282241.733442525</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-4059595.631430879</t>
+          <t>-5726657.861805804</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-33.33</t>
+          <t>-34.07</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>223.045</t>
+          <t>191.359</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.67999999999999</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>103.12</v>
+        <v>102.82</v>
       </c>
       <c r="AV6" t="n">
-        <v>114.79</v>
+        <v>114.05</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>120.98</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-3.97</v>
+        <v>-3.79</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-4.27</v>
+        <v>-4.17</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-131.37</t>
+          <t>-130.67</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>58378540.4</v>
+        <v>49303933.8</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>70706106.9</t>
+          <t>71008822.8</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>80937019.98</v>
+        <v>79031251.22</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-12327566</t>
+          <t>-21704889</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>177730.2094763927</t>
+          <t>-474166.0737401107</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-1253108.279772744</t>
+          <t>-4059595.631430879</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-33.33</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AV7" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>673.665</t>
+          <t>356.655</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AV8" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40.01</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-25.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AV9" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,22 +4507,22 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,22 +4969,22 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-6.23</v>
+        <v>-4.27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AV11" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-4.64</v>
+        <v>-4.56</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1371.211</t>
+          <t>1172.103</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.64</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-24.25</t>
+          <t>-26.79</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>273</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>-3.88</v>
+        <v>-6.23</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-11.15</t>
+          <t>-11.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>105.6</t>
+          <t>104.62</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>105.82</v>
+        <v>105.26</v>
       </c>
       <c r="AV12" t="n">
-        <v>119.1</v>
+        <v>118.29</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>123.24</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-3.84</v>
+        <v>-4.12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-4.76</v>
+        <v>-4.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-135.02</t>
+          <t>-134.08</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>171830439.0485232</t>
+          <t>171645567.3117977</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>63753156.4</v>
+        <v>83033673.40000001</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>50793052.6</t>
+          <t>56976760.5</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>99353698.34</v>
+        <v>93661012</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>12960103</t>
+          <t>26056912</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-6779151.431218925</t>
+          <t>-4445693.973523356</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>5129783.788086943</t>
+          <t>8388322.043802269</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>140543099.0</t>
+          <t>115296140.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-32.33</t>
+          <t>-34.60</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>40.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>13.33</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-9.15</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-7.19</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>98.44</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>100.96</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>111.12</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>119.73</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>8.55</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-3.52</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-3.85</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-128.29</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>26801175.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>30098671.4</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>44238605.9</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>70674096.40000001</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-14139934</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-2872051.905051623</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-5155738.688817903</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>26801175.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-34.40</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.96</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>99.1</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>98.4</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-1.64</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>7.84</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-1.7</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-9.52</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-6.82</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>98.68</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>101.22</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>111.87</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>120.05</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>6.62</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-3.67</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-3.93</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-128.90</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>59596193.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>29159649.8</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>53088102.4</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>73931584</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-23928452</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-2456836.126185026</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-4384238.153662138</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>59596193.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-35.33</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>98.9</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>97.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-2.66</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>14.24</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-2.57</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-9.73</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-6.39</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>99.1</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>101.72</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>112.68</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>120.37</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>8.22</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-3.67</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-4</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-129.37</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>23224556.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>24344852.8</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>61182793.0</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>76121371.45999999</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-36837940</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-2106399.393916461</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-6639266.526523106</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>23224556.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-34.73</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>97.9</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>97.9</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.42</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>23.53</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>18.27</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-0.46</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-2.85</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-9.77</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-6.09</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>99.35999999999999</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>102.27</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>113.34</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>120.69</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>9.24</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-3.7</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-4.08</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-129.98</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>21742310.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>33101836.8</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>63121439.2</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>77659853.2</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-30019602</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-1282241.733442525</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-5726657.861805804</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>21742310.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-34.07</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>98.7</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>98.9</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.10</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>19.19</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>13.12</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.32</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-3.06</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-9.84</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-5.73</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>99.67999999999999</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>102.82</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>114.05</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>120.98</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>9.10</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-3.79</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-4.17</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-130.67</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>19129123.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>49303933.8</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>71008822.8</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>79031251.22</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-21704889</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-474166.0737401107</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-4059595.631430879</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>19129123.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-33.33</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>9.68</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-3.53</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-10.16</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-5.32</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>99.47999999999999</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>103.12</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>114.79</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>121.24</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>7.05</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-3.97</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-4.27</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-131.37</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>22106067.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>58378540.4</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>70706106.9</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>80937019.98</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-12327566</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>177730.2094763927</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-1253108.279772744</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>22106067.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-33.60</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>99.7</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>99.7</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-1.61</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>8.06</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-4.15</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-10.41</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-5.01</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>99.17999999999999</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>103.47</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>115.49</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>121.57</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>5.82</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-4.09</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-4.34</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-131.92</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>35522208.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>77016555</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>70384855.7</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>84490257.36</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>6631699</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>437882.6620671448</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>2481954.94687362</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>35522208.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-33.93</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>98.8</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>99.1</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>2.91</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-1.01</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>8.87</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>11.83</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-0.46</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-3.98</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-10.75</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-4.60</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>99.66</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>103.79</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>116.29</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>121.9</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>6.12</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-4.14</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-4.41</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-132.38</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>67009476.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>98020733.2</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>71152159.5</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>88723869.94</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>26868573</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>66233.15573869471</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>6291674.629694372</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>67009476.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-33.87</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>99.5</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>98.9</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>99.2</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>4.35</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-3.98</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>19.35</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>8.87</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.91</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-2.67</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-10.91</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-4.29</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>101.42</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>104.2</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>116.97</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>122.21</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>7.31</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-4.15</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-4.47</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-132.88</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>102752795.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>93141041.59999999</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>66524111.2</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>90097036.2</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>26616930</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-1065665.294071428</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>8135792.796949223</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>102752795.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-33.00</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>2.82</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>7.26</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>9.67</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-4.27</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-10.98</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-4.02</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>103.42</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>104.68</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>117.59</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>122.51</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>7.13</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-4.23</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-4.56</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-133.48</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>64502156.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>92713711.8</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>58303217.5</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>91495693</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>34410494</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-2738657.674257001</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>6650041.971707948</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>64502156.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-34.00</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>98.9</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>99.7</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>98.1</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>5.06</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.84</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-6.23</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-11.02</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-3.75</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>104.62</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>105.26</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>118.29</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>122.9</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>11.05</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-4.12</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-4.64</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>13.61</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-134.08</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/24</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>171645567.3117977</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>115296140.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>83033673.40000001</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>56976760.5</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>93661012</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>26056912</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-4445693.973523356</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>8388322.043802269</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>115296140.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>150.0</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/09/03</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-34.60</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>豐達科</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>鋼鐵工業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>5.250774319168377</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>25.47364171666412</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>14.58538535259029</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>3.06</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>17.69</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>15.67</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>20.64%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>8.51%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>6322</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>豐達科-鋼鐵工業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>97.0</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>98.1</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>50.21</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 鋼鐵 - 運輸工具、螺絲螺帽</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>272.779</t>
+          <t>460.871</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-16.68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-26.57</t>
+          <t>-27.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1153,47 +1153,47 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.04</v>
+        <v>-1.02</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2.5</v>
+        <v>-2.95</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>98.44</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>100.96</v>
+        <v>100.78</v>
       </c>
       <c r="AZ2" t="n">
-        <v>111.12</v>
+        <v>110.37</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>119.73</t>
+          <t>119.44</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-3.52</v>
+        <v>-3.49</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3.85</v>
+        <v>-3.78</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-128.29</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>26801175.0</t>
+          <t>44673169.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>30098671.4</v>
+        <v>35207480.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>44238605.9</t>
+          <t>42255707.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>70674096.40000001</v>
+        <v>69915365.08</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-14139934</t>
+          <t>-7048226</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2872051.905051623</t>
+          <t>-3080427.926767757</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-5155738.688817903</t>
+          <t>-4226496.046206497</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>26801175.0</t>
+          <t>44673169.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-35.47</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>613.459</t>
+          <t>272.779</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-26.57</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,61 +1621,61 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.7</v>
+        <v>-0.04</v>
       </c>
       <c r="AU3" t="n">
         <v>-2.5</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>98.68</t>
+          <t>98.44</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>101.22</v>
+        <v>100.96</v>
       </c>
       <c r="AZ3" t="n">
-        <v>111.87</v>
+        <v>111.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>120.05</t>
+          <t>119.73</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-3.67</v>
+        <v>-3.52</v>
       </c>
       <c r="BD3" t="n">
-        <v>-3.93</v>
+        <v>-3.85</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-128.90</t>
+          <t>-128.29</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>59596193.0</t>
+          <t>26801175.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>29159649.8</v>
+        <v>30098671.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>53088102.4</t>
+          <t>44238605.9</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>73931584</v>
+        <v>70674096.40000001</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-23928452</t>
+          <t>-14139934</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2456836.126185026</t>
+          <t>-2872051.905051623</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-4384238.153662138</t>
+          <t>-5155738.688817903</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>59596193.0</t>
+          <t>26801175.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>235.048</t>
+          <t>613.459</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-60.21</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-26.94</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.21</v>
+        <v>-1.7</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2.57</v>
+        <v>-2.5</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.68</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>101.72</v>
+        <v>101.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>112.68</v>
+        <v>111.87</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>120.37</t>
+          <t>120.05</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="BC4" t="n">
         <v>-3.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>-4</v>
+        <v>-3.93</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-129.37</t>
+          <t>-128.90</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>23224556.0</t>
+          <t>59596193.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>24344852.8</v>
+        <v>29159649.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>61182793.0</t>
+          <t>53088102.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>76121371.45999999</v>
+        <v>73931584</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-36837940</t>
+          <t>-23928452</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2106399.393916461</t>
+          <t>-2456836.126185026</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-6639266.526523106</t>
+          <t>-4384238.153662138</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>23224556.0</t>
+          <t>59596193.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-34.73</t>
+          <t>-35.33</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>218.931</t>
+          <t>235.048</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-47.56</t>
+          <t>-60.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.19</t>
+          <t>-26.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.46</v>
+        <v>-1.21</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>99.35999999999999</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>102.27</v>
+        <v>101.72</v>
       </c>
       <c r="AZ5" t="n">
-        <v>113.34</v>
+        <v>112.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.37</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3.7</v>
+        <v>-3.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>-4.08</v>
+        <v>-4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-129.98</t>
+          <t>-129.37</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>33101836.8</v>
+        <v>24344852.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>63121439.2</t>
+          <t>61182793.0</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>77659853.2</v>
+        <v>76121371.45999999</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-30019602</t>
+          <t>-36837940</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1282241.733442525</t>
+          <t>-2106399.393916461</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-5726657.861805804</t>
+          <t>-6639266.526523106</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-34.07</t>
+          <t>-34.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>191.359</t>
+          <t>218.931</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-47.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-26.19</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,61 +3067,61 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="AU6" t="n">
-        <v>-3.06</v>
+        <v>-2.85</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>99.67999999999999</t>
+          <t>99.35999999999999</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>102.82</v>
+        <v>102.27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>114.05</v>
+        <v>113.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>120.98</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3.79</v>
+        <v>-3.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>-4.17</v>
+        <v>-4.08</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-130.67</t>
+          <t>-129.98</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>49303933.8</v>
+        <v>33101836.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>71008822.8</t>
+          <t>63121439.2</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>79031251.22</v>
+        <v>77659853.2</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-21704889</t>
+          <t>-30019602</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-474166.0737401107</t>
+          <t>-1282241.733442525</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-4059595.631430879</t>
+          <t>-5726657.861805804</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-33.33</t>
+          <t>-34.07</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>223.045</t>
+          <t>191.359</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="AU7" t="n">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.67999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>103.12</v>
+        <v>102.82</v>
       </c>
       <c r="AZ7" t="n">
-        <v>114.79</v>
+        <v>114.05</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>120.98</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-3.97</v>
+        <v>-3.79</v>
       </c>
       <c r="BD7" t="n">
-        <v>-4.27</v>
+        <v>-4.17</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-131.37</t>
+          <t>-130.67</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>58378540.4</v>
+        <v>49303933.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>70706106.9</t>
+          <t>71008822.8</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>80937019.98</v>
+        <v>79031251.22</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-12327566</t>
+          <t>-21704889</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>177730.2094763927</t>
+          <t>-474166.0737401107</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1253108.279772744</t>
+          <t>-4059595.631430879</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-33.33</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,61 +4031,61 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AU8" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="BD8" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,42 +4317,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>356.655</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>673.665</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>99.2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,61 +4513,61 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AU9" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AZ9" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="BD9" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,172 +4814,172 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>99.2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>37.76</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-25.97</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/05/16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.13</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>40.01</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-25.00</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/05/16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,61 +4995,61 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AZ10" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="BD10" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,61 +5477,61 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AZ11" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="BD11" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1172.103</t>
+          <t>653.398</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>59.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.79</t>
+          <t>-26.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-6.23</v>
+        <v>-4.27</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>104.62</t>
+          <t>103.42</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>105.26</v>
+        <v>104.68</v>
       </c>
       <c r="AZ12" t="n">
-        <v>118.29</v>
+        <v>117.59</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.51</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="BD12" t="n">
-        <v>-4.64</v>
+        <v>-4.56</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-134.08</t>
+          <t>-133.48</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>171645567.3117977</t>
+          <t>171498813.0147265</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>83033673.40000001</v>
+        <v>92713711.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>56976760.5</t>
+          <t>58303217.5</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>93661012</v>
+        <v>91495693</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>26056912</t>
+          <t>34410494</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-4445693.973523356</t>
+          <t>-2738657.674257001</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>8388322.043802269</t>
+          <t>6650041.971707948</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>115296140.0</t>
+          <t>64502156.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-34.60</t>
+          <t>-34.00</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.14</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>98.1</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/運輸工具.xlsx
+++ b/Result/checksun_type/運輸工具.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>460.871</t>
+          <t>166.411</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.68</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1153,242 +1153,242 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.02</v>
+        <v>-0.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2.95</v>
+        <v>-3.17</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-8.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>97.38000000000001</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>100.56</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>109.51</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>119.16</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>7.59</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-127.24</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>171292607.8361345</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>16178877.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>34094794</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>33598315.4</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>62953951.82</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>496478</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-3469198.352684001</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-5607435.695223346</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>16178877.0</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>-35.47</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>豐達科</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>5.250774319168377</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>25.47364171666412</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>14.58538535259029</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>17.69</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>15.41</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>20.64%</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>30.04</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>6219</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>豐達科-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
           <t>97.8</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>100.78</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>110.37</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>119.44</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>7.62</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-3.49</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-3.78</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-127.76</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>171498813.0147265</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>44673169.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>35207480.6</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>42255707.2</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>69915365.08</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-7048226</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-3080427.926767757</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-4226496.046206497</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>44673169.0</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-35.47</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>豐達科</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>5.250774319168377</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>25.47364171666412</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>14.58538535259029</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>17.69</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>15.41</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>20.64%</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>8.51%</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>30.14</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>6219</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>航太扣件及航太車削件88.83%、工業扣件11.17% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>豐達科-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>272.779</t>
+          <t>460.871</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.96</t>
+          <t>-16.68</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.57</t>
+          <t>-27.76</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1635,47 +1635,47 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.04</v>
+        <v>-1.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>-2.5</v>
+        <v>-2.95</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>98.44</t>
+          <t>97.8</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>100.96</v>
+        <v>100.78</v>
       </c>
       <c r="AZ3" t="n">
-        <v>111.12</v>
+        <v>110.37</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>119.73</t>
+          <t>119.44</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-3.52</v>
+        <v>-3.49</v>
       </c>
       <c r="BD3" t="n">
-        <v>-3.85</v>
+        <v>-3.78</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-128.29</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>26801175.0</t>
+          <t>44673169.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>30098671.4</v>
+        <v>35207480.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>44238605.9</t>
+          <t>42255707.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>70674096.40000001</v>
+        <v>69915365.08</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-14139934</t>
+          <t>-7048226</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2872051.905051623</t>
+          <t>-3080427.926767757</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-5155738.688817903</t>
+          <t>-4226496.046206497</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>26801175.0</t>
+          <t>44673169.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-34.40</t>
+          <t>-35.47</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.1</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>98.4</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>613.459</t>
+          <t>272.779</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-31.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>-26.57</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,61 +2103,61 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.7</v>
+        <v>-0.04</v>
       </c>
       <c r="AU4" t="n">
         <v>-2.5</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>98.68</t>
+          <t>98.44</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>101.22</v>
+        <v>100.96</v>
       </c>
       <c r="AZ4" t="n">
-        <v>111.87</v>
+        <v>111.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>120.05</t>
+          <t>119.73</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-3.67</v>
+        <v>-3.52</v>
       </c>
       <c r="BD4" t="n">
-        <v>-3.93</v>
+        <v>-3.85</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-128.90</t>
+          <t>-128.29</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>59596193.0</t>
+          <t>26801175.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>29159649.8</v>
+        <v>30098671.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>53088102.4</t>
+          <t>44238605.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>73931584</v>
+        <v>70674096.40000001</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-23928452</t>
+          <t>-14139934</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2456836.126185026</t>
+          <t>-2872051.905051623</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-4384238.153662138</t>
+          <t>-5155738.688817903</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>59596193.0</t>
+          <t>26801175.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-35.33</t>
+          <t>-34.40</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>98.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>235.048</t>
+          <t>613.459</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-60.21</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-26.94</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.21</v>
+        <v>-1.7</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2.57</v>
+        <v>-2.5</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>98.68</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>101.72</v>
+        <v>101.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>112.68</v>
+        <v>111.87</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>120.37</t>
+          <t>120.05</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="BC5" t="n">
         <v>-3.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>-4</v>
+        <v>-3.93</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-129.37</t>
+          <t>-128.90</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>23224556.0</t>
+          <t>59596193.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>24344852.8</v>
+        <v>29159649.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>61182793.0</t>
+          <t>53088102.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>76121371.45999999</v>
+        <v>73931584</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-36837940</t>
+          <t>-23928452</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2106399.393916461</t>
+          <t>-2456836.126185026</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-6639266.526523106</t>
+          <t>-4384238.153662138</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>23224556.0</t>
+          <t>59596193.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-34.73</t>
+          <t>-35.33</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
           <t>99.6</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>218.931</t>
+          <t>235.048</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-47.56</t>
+          <t>-60.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-26.19</t>
+          <t>-26.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,61 +3067,61 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>14.24</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.46</v>
+        <v>-1.21</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.85</v>
+        <v>-2.57</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>99.35999999999999</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>102.27</v>
+        <v>101.72</v>
       </c>
       <c r="AZ6" t="n">
-        <v>113.34</v>
+        <v>112.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.37</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3.7</v>
+        <v>-3.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>-4.08</v>
+        <v>-4</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-129.98</t>
+          <t>-129.37</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>33101836.8</v>
+        <v>24344852.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>63121439.2</t>
+          <t>61182793.0</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>77659853.2</v>
+        <v>76121371.45999999</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-30019602</t>
+          <t>-36837940</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1282241.733442525</t>
+          <t>-2106399.393916461</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-5726657.861805804</t>
+          <t>-6639266.526523106</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>21742310.0</t>
+          <t>23224556.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-34.07</t>
+          <t>-34.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>191.359</t>
+          <t>218.931</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.57</t>
+          <t>-47.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-25.37</t>
+          <t>-26.19</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.32</v>
+        <v>-0.46</v>
       </c>
       <c r="AU7" t="n">
-        <v>-3.06</v>
+        <v>-2.85</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>99.67999999999999</t>
+          <t>99.35999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>102.82</v>
+        <v>102.27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>114.05</v>
+        <v>113.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>120.98</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-3.79</v>
+        <v>-3.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>-4.17</v>
+        <v>-4.08</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-130.67</t>
+          <t>-129.98</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>49303933.8</v>
+        <v>33101836.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>71008822.8</t>
+          <t>63121439.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>79031251.22</v>
+        <v>77659853.2</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-21704889</t>
+          <t>-30019602</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-474166.0737401107</t>
+          <t>-1282241.733442525</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-4059595.631430879</t>
+          <t>-5726657.861805804</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>19129123.0</t>
+          <t>21742310.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-33.33</t>
+          <t>-34.07</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>98.7</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>223.045</t>
+          <t>191.359</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-30.57</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-25.67</t>
+          <t>-25.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,61 +4031,61 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>-3.53</v>
+        <v>-3.06</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-5.32</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>99.47999999999999</t>
+          <t>99.67999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>103.12</v>
+        <v>102.82</v>
       </c>
       <c r="AZ8" t="n">
-        <v>114.79</v>
+        <v>114.05</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>121.24</t>
+          <t>120.98</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-3.97</v>
+        <v>-3.79</v>
       </c>
       <c r="BD8" t="n">
-        <v>-4.27</v>
+        <v>-4.17</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-131.37</t>
+          <t>-130.67</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>58378540.4</v>
+        <v>49303933.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>70706106.9</t>
+          <t>71008822.8</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>80937019.98</v>
+        <v>79031251.22</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-12327566</t>
+          <t>-21704889</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>177730.2094763927</t>
+          <t>-474166.0737401107</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1253108.279772744</t>
+          <t>-4059595.631430879</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>22106067.0</t>
+          <t>19129123.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-33.60</t>
+          <t>-33.33</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>356.655</t>
+          <t>223.045</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-26.04</t>
+          <t>-25.67</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,61 +4513,61 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AU9" t="n">
-        <v>-4.15</v>
+        <v>-3.53</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-10.41</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>99.17999999999999</t>
+          <t>99.47999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>103.47</v>
+        <v>103.12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>115.49</v>
+        <v>114.79</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>121.57</t>
+          <t>121.24</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="BD9" t="n">
-        <v>-4.34</v>
+        <v>-4.27</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-131.92</t>
+          <t>-131.37</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>77016555</v>
+        <v>58378540.4</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>70384855.7</t>
+          <t>70706106.9</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>84490257.36</v>
+        <v>80937019.98</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>6631699</t>
+          <t>-12327566</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>437882.6620671448</t>
+          <t>177730.2094763927</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>2481954.94687362</t>
+          <t>-1253108.279772744</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>35522208.0</t>
+          <t>22106067.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-33.93</t>
+          <t>-33.60</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>99.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,42 +4799,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>356.655</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>99.1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-2.38</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>673.665</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>99.2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-25.97</t>
+          <t>-26.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,61 +4995,61 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="AU10" t="n">
-        <v>-3.98</v>
+        <v>-4.15</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-10.75</t>
+          <t>-10.41</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-4.60</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>99.66</t>
+          <t>99.17999999999999</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>103.79</v>
+        <v>103.47</v>
       </c>
       <c r="AZ10" t="n">
-        <v>116.29</v>
+        <v>115.49</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.57</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4.14</v>
+        <v>-4.09</v>
       </c>
       <c r="BD10" t="n">
-        <v>-4.41</v>
+        <v>-4.34</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-132.38</t>
+          <t>-131.92</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>98020733.2</v>
+        <v>77016555</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>71152159.5</t>
+          <t>70384855.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>88723869.94</v>
+        <v>84490257.36</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>26868573</t>
+          <t>6631699</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>66233.15573869471</t>
+          <t>437882.6620671448</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>6291674.629694372</t>
+          <t>2481954.94687362</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>67009476.0</t>
+          <t>35522208.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-33.93</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>98.9</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>99.2</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1007.621</t>
+          <t>673.665</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,172 +5296,172 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>99.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37.76</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-25.97</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/05/16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>118.0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>100.5</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.82</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>40.01</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-25.00</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/05/16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,61 +5477,61 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.91</v>
+        <v>-0.46</v>
       </c>
       <c r="AU11" t="n">
-        <v>-2.67</v>
+        <v>-3.98</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-10.91</t>
+          <t>-10.75</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>101.42</t>
+          <t>99.66</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>104.2</v>
+        <v>103.79</v>
       </c>
       <c r="AZ11" t="n">
-        <v>116.97</v>
+        <v>116.29</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>122.21</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>-4.47</v>
+        <v>-4.41</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-132.88</t>
+          <t>-132.38</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>93141041.59999999</v>
+        <v>98020733.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>66524111.2</t>
+          <t>71152159.5</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>90097036.2</v>
+        <v>88723869.94</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>26616930</t>
+          <t>26868573</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-1065665.294071428</t>
+          <t>66233.15573869471</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>8135792.796949223</t>
+          <t>6291674.629694372</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>102752795.0</t>
+          <t>67009476.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-33.00</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>98.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>99.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>653.398</t>
+          <t>1007.621</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>59.02</t>
+          <t>40.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-26.12</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-4.27</v>
+        <v>-0.91</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.2</v>
+        <v>-2.67</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-10.91</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>103.42</t>
+          <t>101.42</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>104.68</v>
+        <v>104.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>117.59</v>
+        <v>116.97</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>122.51</t>
+          <t>122.21</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4.23</v>
+        <v>-4.15</v>
       </c>
       <c r="BD12" t="n">
-        <v>-4.56</v>
+        <v>-4.47</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-133.48</t>
+          <t>-132.88</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>171498813.0147265</t>
+          <t>171292607.8361345</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>92713711.8</v>
+        <v>93141041.59999999</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>58303217.5</t>
+          <t>66524111.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>91495693</v>
+        <v>90097036.2</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>34410494</t>
+          <t>26616930</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2738657.674257001</t>
+          <t>-1065665.294071428</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>6650041.971707948</t>
+          <t>8135792.796949223</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>64502156.0</t>
+          <t>102752795.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-34.00</t>
+          <t>-33.00</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>30.14</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
- 